--- a/optim_results.xlsx
+++ b/optim_results.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\desktop-tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57E29087-C428-4C53-8803-3429ADBA2006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6392540-163C-4A25-9DCD-0F6C4D894491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{350978A1-BF14-4745-982C-7D354B8D03B7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{350978A1-BF14-4745-982C-7D354B8D03B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="1d" sheetId="1" r:id="rId1"/>
+    <sheet name="2d" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>values</t>
   </si>
@@ -83,6 +83,108 @@
   </si>
   <si>
     <t>index</t>
+  </si>
+  <si>
+    <t>LSOA 1</t>
+  </si>
+  <si>
+    <t>LSOA 2</t>
+  </si>
+  <si>
+    <t>LSOA 3</t>
+  </si>
+  <si>
+    <t>LAD</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
+  <si>
+    <t>Outliers imputed</t>
+  </si>
+  <si>
+    <t>Re-normalised to LADs</t>
+  </si>
+  <si>
+    <t>Values</t>
+  </si>
+  <si>
+    <t>V_ij</t>
+  </si>
+  <si>
+    <t>LAD total, by year</t>
+  </si>
+  <si>
+    <t>T_j = sum_i(V_ij)</t>
+  </si>
+  <si>
+    <t>Adjustments</t>
+  </si>
+  <si>
+    <t>X_ij</t>
+  </si>
+  <si>
+    <t>Inputs</t>
+  </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Total LAS is conserved</t>
+  </si>
+  <si>
+    <t>sum_i(X_ij) = 0.</t>
+  </si>
+  <si>
+    <t>Non-negativity</t>
+  </si>
+  <si>
+    <t>V_ij + X_ij &gt;= 0</t>
+  </si>
+  <si>
+    <t>Objective function</t>
+  </si>
+  <si>
+    <t>Outlier flags</t>
+  </si>
+  <si>
+    <t>F_ij = True or False</t>
+  </si>
+  <si>
+    <t>Minimise non-outlier adjustment</t>
+  </si>
+  <si>
+    <t>X_ij*(1-F_ij)</t>
+  </si>
+  <si>
+    <t>Minimise curvsture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W_{i, j-1} - 2W_i, j +  W_{i, j+1} </t>
+  </si>
+  <si>
+    <t>W = V + X</t>
+  </si>
+  <si>
+    <t>if one of the three is an outlier</t>
+  </si>
+  <si>
+    <t>Define constraints</t>
+  </si>
+  <si>
+    <t>Define Objective</t>
+  </si>
+  <si>
+    <t>Solve</t>
+  </si>
+  <si>
+    <t>Destandardise</t>
+  </si>
+  <si>
+    <t>Combine with weights p and (1-p)</t>
+  </si>
+  <si>
+    <t>Standardise</t>
   </si>
 </sst>
 </file>
@@ -90,9 +192,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.0000E+00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -105,13 +207,31 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -155,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -165,9 +285,14 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -210,7 +335,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>'1d'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -245,7 +370,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$5</c:f>
+              <c:f>'1d'!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -266,7 +391,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$5</c:f>
+              <c:f>'1d'!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -297,7 +422,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$1</c:f>
+              <c:f>'1d'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -332,7 +457,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$5</c:f>
+              <c:f>'1d'!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -353,7 +478,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$5</c:f>
+              <c:f>'1d'!$F$2:$F$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -384,7 +509,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$J$1</c:f>
+              <c:f>'1d'!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -419,7 +544,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$5</c:f>
+              <c:f>'1d'!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -440,7 +565,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$J$2:$J$5</c:f>
+              <c:f>'1d'!$J$2:$J$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -471,7 +596,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$O$1</c:f>
+              <c:f>'1d'!$O$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -506,7 +631,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$5</c:f>
+              <c:f>'1d'!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -527,7 +652,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$O$2:$O$5</c:f>
+              <c:f>'1d'!$O$2:$O$5</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2037,9 +2162,399 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DEE1894-97EC-40C3-90DC-7CB853C0AF8D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B2">
+        <v>2001</v>
+      </c>
+      <c r="C2">
+        <v>2002</v>
+      </c>
+      <c r="D2">
+        <v>2003</v>
+      </c>
+      <c r="E2">
+        <v>2004</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="13">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
+      <c r="D3" s="14">
+        <v>17</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="14">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>18</v>
+      </c>
+      <c r="E4">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <f>SUM(B3:B5)</f>
+        <v>37</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:E6" si="0">SUM(C3:C5)</f>
+        <v>40</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>2001</v>
+      </c>
+      <c r="C9">
+        <v>2002</v>
+      </c>
+      <c r="D9">
+        <v>2003</v>
+      </c>
+      <c r="E9">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="13">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
+      <c r="D10" s="14">
+        <f>(C10+E10)/2</f>
+        <v>13.5</v>
+      </c>
+      <c r="E10">
+        <f>E3</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="14">
+        <f>C11-(D11-C11)</f>
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ref="E11:E12" si="1">E4</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <f>SUM(B10:B12)</f>
+        <v>41</v>
+      </c>
+      <c r="C13">
+        <f t="shared" ref="C13" si="2">SUM(C10:C12)</f>
+        <v>40</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13" si="3">SUM(D10:D12)</f>
+        <v>43.5</v>
+      </c>
+      <c r="E13">
+        <f t="shared" ref="E13" si="4">SUM(E10:E12)</f>
+        <v>43</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" t="s">
+        <v>40</v>
+      </c>
+      <c r="K15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>2001</v>
+      </c>
+      <c r="C16">
+        <v>2002</v>
+      </c>
+      <c r="D16">
+        <v>2003</v>
+      </c>
+      <c r="E16">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6">
+        <f>B10*B$6/B$13</f>
+        <v>13.536585365853659</v>
+      </c>
+      <c r="C17" s="6">
+        <f>C10*C$6/C$13</f>
+        <v>13</v>
+      </c>
+      <c r="D17" s="6">
+        <f>D10*D$6/D$13</f>
+        <v>14.586206896551724</v>
+      </c>
+      <c r="E17" s="6">
+        <f>E10*E$6/E$13</f>
+        <v>14</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6">
+        <f>B11*B$6/B$13</f>
+        <v>14.439024390243903</v>
+      </c>
+      <c r="C18" s="6">
+        <f>C11*C$6/C$13</f>
+        <v>17</v>
+      </c>
+      <c r="D18" s="6">
+        <f>D11*D$6/D$13</f>
+        <v>19.448275862068964</v>
+      </c>
+      <c r="E18" s="6">
+        <f>E11*E$6/E$13</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="15">
+        <f>B12*B$6/B$13</f>
+        <v>9.0243902439024382</v>
+      </c>
+      <c r="C19" s="15">
+        <f>C12*C$6/C$13</f>
+        <v>10</v>
+      </c>
+      <c r="D19" s="15">
+        <f>D12*D$6/D$13</f>
+        <v>12.96551724137931</v>
+      </c>
+      <c r="E19" s="15">
+        <f>E12*E$6/E$13</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <f>SUM(B17:B19)</f>
+        <v>37</v>
+      </c>
+      <c r="C20">
+        <f t="shared" ref="C20" si="5">SUM(C17:C19)</f>
+        <v>40</v>
+      </c>
+      <c r="D20">
+        <f t="shared" ref="D20" si="6">SUM(D17:D19)</f>
+        <v>47</v>
+      </c>
+      <c r="E20">
+        <f t="shared" ref="E20" si="7">SUM(E17:E19)</f>
+        <v>43</v>
+      </c>
+      <c r="I20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
